--- a/sample_data/sample_inventory.xlsx
+++ b/sample_data/sample_inventory.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\공윤학\Downloads\Inventory_Check_Partner-main\Inventory_Check_Partner-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\공윤학\Downloads\Inventory_Check_Partner-main\Inventory_Check_Partner-main\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFE0512-0109-426C-96DD-22705134AB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4823DA96-248E-41DF-B750-188C53C07E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="MB 불량발생내용" sheetId="1" r:id="rId1"/>
     <sheet name="README" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="172">
   <si>
     <t>A업체 누적 현황 - GitHub 공개용 샘플</t>
   </si>
@@ -134,9 +147,6 @@
     <t>검수대기</t>
   </si>
   <si>
-    <t>3월 4일</t>
-  </si>
-  <si>
     <t>OUT-0006</t>
   </si>
   <si>
@@ -146,9 +156,6 @@
     <t>VD-100005</t>
   </si>
   <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
     <t>OUT-0007</t>
   </si>
   <si>
@@ -158,9 +165,6 @@
     <t>VD-100006</t>
   </si>
   <si>
-    <t>3월 26일</t>
-  </si>
-  <si>
     <t>OUT-0008</t>
   </si>
   <si>
@@ -170,9 +174,6 @@
     <t>VD-100007</t>
   </si>
   <si>
-    <t>3월 29일</t>
-  </si>
-  <si>
     <t>OUT-0009</t>
   </si>
   <si>
@@ -185,15 +186,9 @@
     <t>RMA</t>
   </si>
   <si>
-    <t>4월 17일</t>
-  </si>
-  <si>
     <t>IN-0009</t>
   </si>
   <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
     <t>OUT-0010</t>
   </si>
   <si>
@@ -203,9 +198,6 @@
     <t>VD-100009</t>
   </si>
   <si>
-    <t>4월 24일</t>
-  </si>
-  <si>
     <t>OUT-0011</t>
   </si>
   <si>
@@ -215,9 +207,6 @@
     <t>VD-100010</t>
   </si>
   <si>
-    <t>3월 28일</t>
-  </si>
-  <si>
     <t>OUT-0012</t>
   </si>
   <si>
@@ -230,9 +219,6 @@
     <t>외관 파손</t>
   </si>
   <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
     <t>OUT-0013</t>
   </si>
   <si>
@@ -245,9 +231,6 @@
     <t>IN-0013</t>
   </si>
   <si>
-    <t>4월 14일</t>
-  </si>
-  <si>
     <t>OUT-0014</t>
   </si>
   <si>
@@ -257,9 +240,6 @@
     <t>VD-100013</t>
   </si>
   <si>
-    <t>3월 6일</t>
-  </si>
-  <si>
     <t>OUT-0015</t>
   </si>
   <si>
@@ -269,9 +249,6 @@
     <t>VD-100014</t>
   </si>
   <si>
-    <t>2026-03-16</t>
-  </si>
-  <si>
     <t>OUT-0016</t>
   </si>
   <si>
@@ -284,9 +261,6 @@
     <t>팬 소음</t>
   </si>
   <si>
-    <t>4월 7일</t>
-  </si>
-  <si>
     <t>OUT-0017</t>
   </si>
   <si>
@@ -296,15 +270,9 @@
     <t>VD-100016</t>
   </si>
   <si>
-    <t>4월 23일</t>
-  </si>
-  <si>
     <t>IN-0017</t>
   </si>
   <si>
-    <t>3월 9일</t>
-  </si>
-  <si>
     <t>OUT-0018</t>
   </si>
   <si>
@@ -314,9 +282,6 @@
     <t>VD-100017</t>
   </si>
   <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
     <t>OUT-0019</t>
   </si>
   <si>
@@ -326,9 +291,6 @@
     <t>VD-100018</t>
   </si>
   <si>
-    <t>3월 13일</t>
-  </si>
-  <si>
     <t>OUT-0020</t>
   </si>
   <si>
@@ -338,9 +300,6 @@
     <t>VD-100019</t>
   </si>
   <si>
-    <t>5월 21일</t>
-  </si>
-  <si>
     <t>OUT-0021</t>
   </si>
   <si>
@@ -350,15 +309,9 @@
     <t>VD-100020</t>
   </si>
   <si>
-    <t>6월 6일</t>
-  </si>
-  <si>
     <t>IN-0021</t>
   </si>
   <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
     <t>OUT-0022</t>
   </si>
   <si>
@@ -368,9 +321,6 @@
     <t>VD-100021</t>
   </si>
   <si>
-    <t>5월 27일</t>
-  </si>
-  <si>
     <t>OUT-0023</t>
   </si>
   <si>
@@ -389,9 +339,6 @@
     <t>VD-100023</t>
   </si>
   <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
     <t>OUT-0025</t>
   </si>
   <si>
@@ -401,9 +348,6 @@
     <t>VD-100024</t>
   </si>
   <si>
-    <t>4월 11일</t>
-  </si>
-  <si>
     <t>IN-0025</t>
   </si>
   <si>
@@ -425,9 +369,6 @@
     <t>VD-100026</t>
   </si>
   <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
     <t>OUT-0028</t>
   </si>
   <si>
@@ -437,9 +378,6 @@
     <t>VD-100027</t>
   </si>
   <si>
-    <t>4월 4일</t>
-  </si>
-  <si>
     <t>OUT-0029</t>
   </si>
   <si>
@@ -452,9 +390,6 @@
     <t>IN-0029</t>
   </si>
   <si>
-    <t>4월 10일</t>
-  </si>
-  <si>
     <t>OUT-0030</t>
   </si>
   <si>
@@ -464,9 +399,6 @@
     <t>VD-100029</t>
   </si>
   <si>
-    <t>2026-05-22</t>
-  </si>
-  <si>
     <t>OUT-0031</t>
   </si>
   <si>
@@ -476,9 +408,6 @@
     <t>VD-100030</t>
   </si>
   <si>
-    <t>3월 18일</t>
-  </si>
-  <si>
     <t>OUT-0032</t>
   </si>
   <si>
@@ -488,9 +417,6 @@
     <t>VD-100031</t>
   </si>
   <si>
-    <t>4월 3일</t>
-  </si>
-  <si>
     <t>OUT-0033</t>
   </si>
   <si>
@@ -500,15 +426,9 @@
     <t>VD-100032</t>
   </si>
   <si>
-    <t>4월 21일</t>
-  </si>
-  <si>
     <t>IN-0033</t>
   </si>
   <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
     <t>OUT-0034</t>
   </si>
   <si>
@@ -518,9 +438,6 @@
     <t>VD-100033</t>
   </si>
   <si>
-    <t>3월 12일</t>
-  </si>
-  <si>
     <t>OUT-0035</t>
   </si>
   <si>
@@ -530,9 +447,6 @@
     <t>VD-100034</t>
   </si>
   <si>
-    <t>3월 15일</t>
-  </si>
-  <si>
     <t>OUT-0036</t>
   </si>
   <si>
@@ -542,9 +456,6 @@
     <t>VD-100035</t>
   </si>
   <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
     <t>OUT-0037</t>
   </si>
   <si>
@@ -554,15 +465,9 @@
     <t>VD-100036</t>
   </si>
   <si>
-    <t>6월 14일</t>
-  </si>
-  <si>
     <t>IN-0037</t>
   </si>
   <si>
-    <t>4월 18일</t>
-  </si>
-  <si>
     <t>OUT-0038</t>
   </si>
   <si>
@@ -572,9 +477,6 @@
     <t>VD-100037</t>
   </si>
   <si>
-    <t>4월 2일</t>
-  </si>
-  <si>
     <t>OUT-0039</t>
   </si>
   <si>
@@ -582,9 +484,6 @@
   </si>
   <si>
     <t>VD-100038</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
   </si>
   <si>
     <t>OUT-0040</t>
@@ -659,7 +558,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <numFmts count="1">
+    <numFmt numFmtId="179" formatCode="m&quot;월&quot;\ d&quot;일&quot;;@"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -711,6 +613,12 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -743,7 +651,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -758,25 +666,35 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
-      <font>
-        <b/>
-        <color rgb="FFB91C1C"/>
-      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -784,6 +702,19 @@
           <bgColor rgb="FFFEF3C7"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFB91C1C"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -799,7 +730,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SampleRmaHistory" displayName="SampleRmaHistory" ref="C6:M46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SampleRmaHistory" displayName="SampleRmaHistory" ref="C6:M47">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="업체 출고일"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="출고 송장번호"/>
@@ -811,7 +742,9 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="RMA 수리 후 입고 일"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="입고 송장번호"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="비고"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="소요일"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="소요일" dataDxfId="0">
+      <calculatedColumnFormula>IF(ISBLANK(J7),"0",NETWORKDAYS(IF(C7="이전 자료 품목","2025-01-01",C7),J7))</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -966,7 +899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:M46"/>
+  <dimension ref="C2:M47"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="4" width="16" customWidth="1"/>
@@ -975,33 +908,33 @@
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="13" max="13" width="10" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:13" ht="18">
-      <c r="F2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="F2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
     </row>
     <row r="4" spans="3:13">
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
     </row>
     <row r="6" spans="3:13" ht="21.95" customHeight="1">
       <c r="C6" s="1" t="s">
@@ -1010,11 +943,11 @@
       <c r="D6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>208</v>
+      <c r="E6" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>4</v>
@@ -1060,12 +993,17 @@
       <c r="I7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="3"/>
+      <c r="J7" s="10">
+        <v>45676</v>
+      </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="3"/>
+      <c r="M7" s="13">
+        <f t="shared" ref="M7:M47" si="0">IF(ISBLANK(J7),"0",NETWORKDAYS(IF(C7="이전 자료 품목","2025-01-01",C7),J7))</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="3:13">
       <c r="C8" s="3" t="s">
@@ -1089,12 +1027,17 @@
       <c r="I8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="3"/>
+      <c r="J8" s="10">
+        <v>45677</v>
+      </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="3"/>
+      <c r="M8" s="13">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="3:13">
       <c r="C9" s="3" t="s">
@@ -1118,14 +1061,19 @@
       <c r="I9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="3"/>
+      <c r="J9" s="10">
+        <v>45677</v>
+      </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="3:13">
+      <c r="M9" s="13">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="3:13" ht="15">
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
@@ -1147,14 +1095,19 @@
       <c r="I10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="3"/>
+      <c r="J10" s="10">
+        <v>45738</v>
+      </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="3:13">
+      <c r="M10" s="13">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="3:13" ht="15">
       <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
@@ -1176,28 +1129,33 @@
       <c r="I11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="3"/>
+      <c r="J11" s="10">
+        <v>45739</v>
+      </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="3:13">
-      <c r="C12" s="3" t="s">
+      <c r="M11" s="13">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="3:13" ht="15">
+      <c r="C12" s="11">
+        <v>46085</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="E12" s="3">
         <v>18014502</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>15</v>
@@ -1210,23 +1168,26 @@
       <c r="L12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="3:13">
-      <c r="C13" s="3" t="s">
-        <v>41</v>
+      <c r="M12" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:13" ht="15">
+      <c r="C13" s="11">
+        <v>46146</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E13" s="3">
         <v>18014840</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>35</v>
@@ -1239,23 +1200,26 @@
       <c r="L13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="3:13">
-      <c r="C14" s="3" t="s">
-        <v>45</v>
+      <c r="M13" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:13" ht="15">
+      <c r="C14" s="11">
+        <v>46107</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E14" s="3">
         <v>18015702</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>30</v>
@@ -1268,58 +1232,62 @@
       <c r="L14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M14" s="3"/>
+      <c r="M14" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="3:13" ht="15">
-      <c r="C15" s="3" t="s">
-        <v>49</v>
+      <c r="C15" s="11">
+        <v>46110</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E15" s="3">
         <v>18015695</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
+      </c>
+      <c r="J15" s="10">
+        <v>46165</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M15" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="3:13">
-      <c r="C16" s="3" t="s">
-        <v>56</v>
+      <c r="M15" s="13">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="3:13" ht="15">
+      <c r="C16" s="11">
+        <v>46193</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E16" s="3">
         <v>18016219</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
@@ -1332,145 +1300,158 @@
       <c r="L16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13">
-      <c r="C17" s="3" t="s">
-        <v>60</v>
+      <c r="M16" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" ht="15">
+      <c r="C17" s="11">
+        <v>46136</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E17" s="3">
         <v>18015902</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13">
-      <c r="C18" s="3" t="s">
-        <v>64</v>
+      <c r="M17" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" ht="15">
+      <c r="C18" s="11">
+        <v>46109</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E18" s="3">
         <v>18014534</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="3"/>
+      <c r="M18" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="3:13" ht="15">
-      <c r="C19" s="3" t="s">
-        <v>69</v>
+      <c r="C19" s="11">
+        <v>46093</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E19" s="3">
         <v>18014517</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J19" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="J19" s="10">
+        <v>46196</v>
+      </c>
       <c r="K19" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M19" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="3:13">
-      <c r="C20" s="3" t="s">
+      <c r="M19" s="13">
+        <f t="shared" si="0"/>
         <v>74</v>
       </c>
+    </row>
+    <row r="20" spans="3:13" ht="15">
+      <c r="C20" s="11">
+        <v>46126</v>
+      </c>
       <c r="D20" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3">
         <v>18016430</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13">
-      <c r="C21" s="3" t="s">
-        <v>78</v>
+      <c r="M20" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" ht="15">
+      <c r="C21" s="11">
+        <v>46087</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E21" s="3">
         <v>18016219</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
@@ -1483,26 +1464,29 @@
       <c r="L21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13">
-      <c r="C22" s="3" t="s">
-        <v>82</v>
+      <c r="M21" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" ht="15">
+      <c r="C22" s="11">
+        <v>46097</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E22" s="3">
         <v>18015702</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>16</v>
@@ -1512,23 +1496,26 @@
       <c r="L22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M22" s="3"/>
+      <c r="M22" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="3:13" ht="15">
-      <c r="C23" s="3" t="s">
-        <v>87</v>
+      <c r="C23" s="11">
+        <v>46119</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E23" s="3">
         <v>18015702</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>35</v>
@@ -1536,34 +1523,35 @@
       <c r="I23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>91</v>
+      <c r="J23" s="10">
+        <v>46201</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="3:13">
-      <c r="C24" s="3" t="s">
-        <v>93</v>
+      <c r="M23" s="13">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" ht="15">
+      <c r="C24" s="11">
+        <v>46090</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E24" s="3">
         <v>18015902</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>15</v>
@@ -1576,23 +1564,26 @@
       <c r="L24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13">
-      <c r="C25" s="3" t="s">
-        <v>97</v>
+      <c r="M24" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" ht="15">
+      <c r="C25" s="11">
+        <v>46119</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E25" s="3">
         <v>18016219</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>15</v>
@@ -1605,116 +1596,126 @@
       <c r="L25" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13">
-      <c r="C26" s="3" t="s">
-        <v>101</v>
+      <c r="M25" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" ht="15">
+      <c r="C26" s="11">
+        <v>46094</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="E26" s="3">
         <v>18016430</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M26" s="3"/>
+      <c r="M26" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="3:13" ht="15">
-      <c r="C27" s="3" t="s">
-        <v>105</v>
+      <c r="C27" s="11">
+        <v>46023</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="E27" s="3">
         <v>18015701</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>109</v>
+        <v>49</v>
+      </c>
+      <c r="J27" s="10">
+        <v>46144</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M27" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="3:13">
-      <c r="C28" s="3" t="s">
-        <v>111</v>
+      <c r="M27" s="13">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" ht="15">
+      <c r="C28" s="11">
+        <v>46108</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="E28" s="3">
         <v>18015682</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13">
-      <c r="C29" s="3" t="s">
-        <v>115</v>
+      <c r="M28" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" ht="15">
+      <c r="C29" s="11">
+        <v>46169</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="E29" s="3">
         <v>18015902</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>30</v>
@@ -1727,23 +1728,26 @@
       <c r="L29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13">
-      <c r="C30" s="3" t="s">
-        <v>105</v>
+      <c r="M29" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" ht="15">
+      <c r="C30" s="11">
+        <v>46163</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="E30" s="3">
         <v>18015886</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>26</v>
@@ -1756,58 +1760,62 @@
       <c r="L30" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13">
-      <c r="C31" s="3" t="s">
-        <v>122</v>
+      <c r="M30" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" ht="15">
+      <c r="C31" s="11">
+        <v>46113</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="E31" s="3">
         <v>18015902</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>126</v>
+      <c r="J31" s="10">
+        <v>46243</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M31" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="3:13">
-      <c r="C32" s="3" t="s">
+      <c r="M31" s="13">
+        <f t="shared" si="0"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" ht="15">
+      <c r="C32" s="11">
+        <v>46163</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="E32" s="3">
         <v>18015680</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>30</v>
@@ -1820,23 +1828,26 @@
       <c r="L32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="3:13">
-      <c r="C33" s="3" t="s">
-        <v>115</v>
+      <c r="M32" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:13" ht="15">
+      <c r="C33" s="11">
+        <v>46169</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E33" s="3">
         <v>18014840</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>21</v>
@@ -1849,52 +1860,58 @@
       <c r="L33" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="3:13">
-      <c r="C34" s="3" t="s">
-        <v>134</v>
+      <c r="M33" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:13" ht="15">
+      <c r="C34" s="11">
+        <v>46187</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="E34" s="3">
         <v>18014840</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="3:13">
-      <c r="C35" s="3" t="s">
-        <v>138</v>
+      <c r="M34" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:13" ht="15">
+      <c r="C35" s="11">
+        <v>46026</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="E35" s="3">
         <v>18015695</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>26</v>
@@ -1902,34 +1919,35 @@
       <c r="I35" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>126</v>
+      <c r="J35" s="10">
+        <v>46068</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M35" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="3:13">
-      <c r="C36" s="3" t="s">
-        <v>143</v>
+      <c r="M35" s="13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="3:13" ht="15">
+      <c r="C36" s="11">
+        <v>46122</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="E36" s="3">
         <v>18015902</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>26</v>
@@ -1942,26 +1960,29 @@
       <c r="L36" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M36" s="3"/>
-    </row>
-    <row r="37" spans="3:13">
-      <c r="C37" s="3" t="s">
-        <v>147</v>
+      <c r="M36" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:13" ht="15">
+      <c r="C37" s="11">
+        <v>46164</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="E37" s="3">
         <v>18015695</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>22</v>
@@ -1971,23 +1992,26 @@
       <c r="L37" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M37" s="3"/>
-    </row>
-    <row r="38" spans="3:13">
-      <c r="C38" s="3" t="s">
-        <v>151</v>
+      <c r="M37" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="3:13" ht="15">
+      <c r="C38" s="11">
+        <v>46099</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="E38" s="3">
         <v>18015680</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>26</v>
@@ -2000,23 +2024,26 @@
       <c r="L38" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="3"/>
+      <c r="M38" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="39" spans="3:13" ht="15">
-      <c r="C39" s="3" t="s">
-        <v>155</v>
+      <c r="C39" s="11">
+        <v>46025</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="E39" s="3">
         <v>18015702</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>35</v>
@@ -2024,34 +2051,35 @@
       <c r="I39" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>159</v>
+      <c r="J39" s="10">
+        <v>46054</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M39" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="3:13">
-      <c r="C40" s="3" t="s">
-        <v>161</v>
+      <c r="M39" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="3:13" ht="15">
+      <c r="C40" s="11">
+        <v>46110</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="E40" s="3">
         <v>18015682</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>26</v>
@@ -2064,26 +2092,29 @@
       <c r="L40" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="3:13">
-      <c r="C41" s="3" t="s">
-        <v>165</v>
+      <c r="M40" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="3:13" ht="15">
+      <c r="C41" s="11">
+        <v>46093</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="E41" s="3">
         <v>18015701</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>16</v>
@@ -2093,23 +2124,26 @@
       <c r="L41" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="3:13">
-      <c r="C42" s="3" t="s">
-        <v>169</v>
+      <c r="M41" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="3:13" ht="15">
+      <c r="C42" s="11">
+        <v>46096</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="E42" s="3">
         <v>18016430</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>26</v>
@@ -2122,23 +2156,26 @@
       <c r="L42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M42" s="3"/>
+      <c r="M42" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="3:13" ht="15">
-      <c r="C43" s="3" t="s">
-        <v>173</v>
+      <c r="C43" s="11">
+        <v>46169</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="E43" s="3">
         <v>18016219</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>35</v>
@@ -2146,34 +2183,35 @@
       <c r="I43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>177</v>
+      <c r="J43" s="10">
+        <v>46365</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="3:13">
-      <c r="C44" s="3" t="s">
-        <v>179</v>
+      <c r="M43" s="13">
+        <f t="shared" si="0"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="3:13" ht="15">
+      <c r="C44" s="11">
+        <v>46130</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="E44" s="3">
         <v>18015695</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>35</v>
@@ -2186,23 +2224,26 @@
       <c r="L44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="3:13">
-      <c r="C45" s="3" t="s">
-        <v>183</v>
+      <c r="M44" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="3:13" ht="15">
+      <c r="C45" s="11">
+        <v>46114</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="E45" s="3">
         <v>18015702</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>35</v>
@@ -2215,23 +2256,26 @@
       <c r="L45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="3:13">
-      <c r="C46" s="3" t="s">
-        <v>187</v>
+      <c r="M45" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="3:13" ht="15">
+      <c r="C46" s="11">
+        <v>46174</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="E46" s="3">
         <v>18015887</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>15</v>
@@ -2244,7 +2288,16 @@
       <c r="L46" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M46" s="3"/>
+      <c r="M46" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:13" ht="15">
+      <c r="M47" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2252,13 +2305,13 @@
     <mergeCell ref="C4:M4"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="J7:J46">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="J7:J47">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>ISBLANK(J7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M46">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="M7:M47">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
       <formula>15</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2280,71 +2333,71 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.25">
       <c r="A1" s="4" t="s">
-        <v>191</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="5" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15">
       <c r="A4" s="5" t="s">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15">
       <c r="A5" s="5" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>197</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15">
       <c r="A6" s="5" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15">
       <c r="A7" s="5" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>201</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15">
       <c r="A8" s="5" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15">
       <c r="A9" s="5" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15">
       <c r="A10" s="5" t="s">
-        <v>206</v>
+        <v>168</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
